--- a/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pasteurización" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mantecación" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pasteurización" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantecación" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Pasteurización'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mantecación'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -150,54 +158,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -557,15 +576,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -573,6 +593,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -601,9 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -632,8 +651,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -642,18 +678,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,6 +706,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -790,6 +827,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -910,6 +948,7 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -1048,6 +1087,26 @@
       <c r="E24" s="12" t="n"/>
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C25">
+        <f>COUNTIF(E6:E24,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E25">
+        <f>COUNTIF(B6:B24,"?*")</f>
+        <v>15.0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -1073,12 +1132,26 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23 E24" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1087,18 +1160,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1115,6 +1188,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1235,6 +1309,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1374,6 +1449,7 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -1512,6 +1588,26 @@
       <c r="E25" s="12" t="n"/>
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>COUNTIF(E6:E25,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E26">
+        <f>COUNTIF(B6:B25,"?*")</f>
+        <v>16.0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -1537,11 +1633,25 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
@@ -90,7 +90,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -133,8 +133,13 @@
         <bgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -156,11 +161,55 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +251,17 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -578,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -653,9 +713,38 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Vida útil y caducidades:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «Mantecación» tienes una tabla editable de vida útil por familia: ajústala a tu producto y a tu proveedor. Está fuera del contador porque es una referencia, no una tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ La mezcla base pasteurizada NO se congela: se madura a 2-4 °C y se manteca en 3-5 días. Lo que se congela es el producto terminado, a −18 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -878,7 +967,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Pasteurizar a 85°C durante 15 segundos (alta pasteurización)</t>
+          <t>Pasteurizar a 85 °C durante 15 segundos (alta pasteurización)</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -897,7 +986,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Añadir grasas y emulsionantes al alcanzar 40-50°C en descenso</t>
+          <t>Añadir grasas y emulsionantes al alcanzar 40-50 °C en descenso</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -916,7 +1005,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Enfriar rápidamente a 4°C en abatidor o ciclo de enfriamiento</t>
+          <t>Enfriar rápidamente a 4 °C en abatidor o ciclo de enfriamiento</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -935,7 +1024,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperatura final de la mezcla (&lt;4°C)</t>
+          <t>Verificar temperatura final de la mezcla (&lt;4 °C)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1037,7 +1126,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Respetar tiempo de maduración: mínimo 4h, óptimo 8-12h a 2-4°C</t>
+          <t>Respetar tiempo de maduración: mínimo 4h, óptimo 8-12h a 2-4 °C</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -1095,8 +1184,8 @@
         </is>
       </c>
       <c r="C25">
-        <f>COUNTIF(E6:E24,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B24,"?*",E6:E24,"✓")-COUNTIFS(B6:B24,"Tarea",E6:E24,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1104,8 +1193,8 @@
         </is>
       </c>
       <c r="E25">
-        <f>COUNTIF(B6:B24,"?*")</f>
-        <v>15.0</v>
+        <f>COUNTIF(B6:B24,"?*")-COUNTIF(B6:B24,"Tarea")-COUNTIF(E6:E24,"N/A")</f>
+        <v>13.0</v>
       </c>
     </row>
     <row r="26">
@@ -1138,8 +1227,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1162,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1366,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Programar mantecadora: crema -7°C/-9°C | sorbete -10°C/-12°C</t>
+          <t>Programar mantecadora: crema −7 °C/−9 °C | sorbete −10 °C/−12 °C</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1296,7 +1385,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Preparar cubetas pre-enfriadas en congelador (-20°C)</t>
+          <t>Preparar cubetas pre-enfriadas en congelador (−20 °C)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1417,7 +1506,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Etiquetar cubeta: sabor, fecha producción, caducidad, lote</t>
+          <t>Etiquetar cubeta: sabor, fecha de producción, caducidad y lote — la vida útil por familia está en la tabla del pie de esta hoja</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1500,7 +1589,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Abatir cubeta a -18°C en abatidor (ciclo de congelación)</t>
+          <t>Abatir cubeta a −18 °C en abatidor (ciclo de congelación)</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -1519,7 +1608,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Trasladar cubeta a cámara de conservación -18°C/-20°C</t>
+          <t>Trasladar cubeta a cámara de conservación −18 °C/−20 °C</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -1596,8 +1685,8 @@
         </is>
       </c>
       <c r="C26">
-        <f>COUNTIF(E6:E25,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B25,"?*",E6:E25,"✓")-COUNTIFS(B6:B25,"Tarea",E6:E25,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1605,8 +1694,8 @@
         </is>
       </c>
       <c r="E26">
-        <f>COUNTIF(B6:B25,"?*")</f>
-        <v>16.0</v>
+        <f>COUNTIF(B6:B25,"?*")-COUNTIF(B6:B25,"Tarea")-COUNTIF(E6:E25,"N/A")</f>
+        <v>14.0</v>
       </c>
     </row>
     <row r="27">
@@ -1617,21 +1706,186 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA — ajústala a tu producto, a tu maquinaria y a tu proveedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Helado y sorbete artesanal en cubeta tapada</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>2-3 meses a −18 °C</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>En vitrina de servicio la calidad cae en 3-5 días: rota por sabor, no por la fecha larga de la cámara</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Mezcla base pasteurizada, sin mantecar</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>3-5 días a 2-4 °C</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>La base no se congela: al descongelar se separa y pierde estructura</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Tarta helada y semifrío montados</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>1 mes a −18 °C</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Envueltos y en caja: absorben el olor de la cámara con una facilidad enorme</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Fruta y purés de fruta congelados</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>6-12 meses a −18 °C</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Congela en porciones de un solo uso: descongelar y volver a congelar no se hace</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Frutos secos, pastas y pralinés</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>6 meses a −18 °C · 2-3 meses en frío</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>La grasa del fruto seco se enrancia sin avisar: fecha de apertura en el bote, siempre</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Variegatos, salsas y toppings abiertos</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Lo que diga el fabricante</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>El plazo cuenta desde la APERTURA: anótala en el envase el mismo día</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="15">
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D31:G31"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D33:G33"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="D32:G32"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D34:G34"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G25">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -1639,8 +1893,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/02-partidas-produccion.xlsx
@@ -1872,8 +1872,8 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="D36:G36"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="D31:G31"/>
-    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="A27:G27"/>
